--- a/metrics/Global_Metrics_Ablation_Study_VPD.xlsx
+++ b/metrics/Global_Metrics_Ablation_Study_VPD.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.736380629550284</v>
+        <v>2.574061437406105</v>
       </c>
       <c r="C2" t="n">
-        <v>2.481581513670772</v>
+        <v>2.2399557315855</v>
       </c>
       <c r="D2" t="n">
-        <v>10.35229224105723</v>
+        <v>9.538102127236131</v>
       </c>
       <c r="E2" t="n">
-        <v>3.217497823007379</v>
+        <v>3.08838179751729</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8701611457034745</v>
+        <v>0.8928707515115742</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9328729650499903</v>
+        <v>0.9449947102762352</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9355306037481774</v>
+        <v>0.9456146047859186</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7820722461690448</v>
+        <v>0.8049444487834868</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0110240702035711</v>
+        <v>4.152704837500301</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1253275376154213</v>
+        <v>4.92126548574787</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4689333892273657</v>
+        <v>21.11746236667347</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4701688561848218</v>
+        <v>4.59537401814841</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3891878567867206</v>
+        <v>0.7731270829621992</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1210766407980033</v>
+        <v>0.9692768461905471</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1281695269600884</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9725578637541702</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8828918946902234</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.112512248556851</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.912415948890993</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.375959868524466</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.525066309728215</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9139272315489338</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9621780056686831</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9566103431704763</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8321883749009319</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.274650131563143</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.12301664219627</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>7.209030987500569</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.68496387079986</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.914190901096403</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.9651295613883096</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9658108018919109</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8510977811566196</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.02112115156063538</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.2148191853536314</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.01113303178785691</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.01203952723460028</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.02457934903371067</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.2247514677427245</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.1870440106386499</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3536223752249569</v>
+        <v>0.376104741227199</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2454870735523577</v>
+        <v>0.2626182993662955</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2367383594799264</v>
+        <v>0.2641552418049722</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4865576630574493</v>
+        <v>0.5139603504210926</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9577796208067239</v>
+        <v>0.9578551171424676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9808019861700874</v>
+        <v>0.9814785167400729</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9845245739291131</v>
+        <v>0.9827310032069531</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8943565745418296</v>
+        <v>0.8905841293185276</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005996335936657715</v>
+        <v>0.3593232554115426</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03254657850229514</v>
+        <v>0.3039268050078303</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4905029061805977</v>
+        <v>0.1886570505825254</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4910814240043495</v>
+        <v>0.434346693992858</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4429907340492876</v>
+        <v>0.9661581131241779</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02640348065034726</v>
+        <v>0.9830061031275147</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0209293619232646</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9830102831329589</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9013831404189323</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2294764745365221</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1727458545440061</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1038126066856309</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3221996379352884</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.964889774658739</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9882120274101895</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9866462979223225</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.9040262992039249</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.4694569774058571</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3951380646442417</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.3870196231469577</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.62210901226952</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9443750566993997</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9848262140834892</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9873949040242117</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.9084672570494431</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.009271675378156707</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05295056619902674</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.004264986608381593</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.005522173181375711</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01655931797455595</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.04891435741246367</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.06112199567548286</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.129528852812026</v>
+        <v>1.142793383770129</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8271777968467848</v>
+        <v>0.7268230843974273</v>
       </c>
       <c r="D4" t="n">
-        <v>2.430828640582961</v>
+        <v>2.582617351169738</v>
       </c>
       <c r="E4" t="n">
-        <v>1.559111490748164</v>
+        <v>1.607052379721874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9616151538093655</v>
+        <v>0.963468777753208</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9807420241741406</v>
+        <v>0.9815840941332216</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9792779487076673</v>
+        <v>0.9765262138292944</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8816976492330247</v>
+        <v>0.8764834591268671</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004763873602235513</v>
+        <v>1.573063411809082</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1036180721763879</v>
+        <v>1.513772121750049</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4916596391322609</v>
+        <v>3.879805230376313</v>
       </c>
       <c r="M4" t="n">
-        <v>0.487903415239805</v>
+        <v>1.969722120091134</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4347802277832865</v>
+        <v>0.9539231320599475</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07912319541357304</v>
+        <v>0.9782346789341552</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09919575572359984</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9775866522140891</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.8942495636365952</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.181271945941784</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7065772988894237</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1094528966451</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.763364085106959</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9237931507751125</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9680099617698642</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9584173372446974</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.840197165740927</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.9634352208769617</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.6234666686707691</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.79742374820019</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.340680330354775</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9769828495127181</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9885893275249475</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.9843370143468184</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9038490925021083</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.008646410691694417</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1805996414170147</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.00432281477927926</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.006191388857546387</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01418688922502137</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1342489459107751</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.1470084664703627</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
